--- a/data/attractions.xlsx
+++ b/data/attractions.xlsx
@@ -1,19 +1,44 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>12.0000</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>
+  </dc:creator>
+  <cp:lastModifiedBy>
+  </cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-17T16:50:08Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-17T17:28:59Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3394" uniqueCount="1177">
   <si>
     <t>Pays</t>
@@ -3549,7 +3574,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
@@ -3617,7 +3642,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -3900,7 +3925,21 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1131"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/data/attractions.xlsx
+++ b/data/attractions.xlsx
@@ -378,7 +378,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="9" min="1" max="1"/>
@@ -8050,26 +8050,406 @@
         <v>12</v>
       </c>
     </row>
-    <row r="384" ht="15.75" customHeight="1" s="9"/>
-    <row r="385" ht="15.75" customHeight="1" s="9"/>
-    <row r="386" ht="15.75" customHeight="1" s="9"/>
-    <row r="387" ht="15.75" customHeight="1" s="9"/>
-    <row r="388" ht="15.75" customHeight="1" s="9"/>
-    <row r="389" ht="15.75" customHeight="1" s="9"/>
-    <row r="390" ht="15.75" customHeight="1" s="9"/>
-    <row r="391" ht="15.75" customHeight="1" s="9"/>
-    <row r="392" ht="15.75" customHeight="1" s="9"/>
-    <row r="393" ht="15.75" customHeight="1" s="9"/>
-    <row r="394" ht="15.75" customHeight="1" s="9"/>
-    <row r="395" ht="15.75" customHeight="1" s="9"/>
-    <row r="396" ht="15.75" customHeight="1" s="9"/>
-    <row r="397" ht="15.75" customHeight="1" s="9"/>
-    <row r="398" ht="15.75" customHeight="1" s="9"/>
-    <row r="399" ht="15.75" customHeight="1" s="9"/>
-    <row r="400" ht="15.75" customHeight="1" s="9"/>
-    <row r="401" ht="15.75" customHeight="1" s="9"/>
-    <row r="402" ht="15.75" customHeight="1" s="9"/>
-    <row r="403" ht="15.75" customHeight="1" s="9"/>
+    <row r="384" ht="15.75" customHeight="1" s="9">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Universal Epic Universe</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Harry Potter and the Battle at the Ministry</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="385" ht="15.75" customHeight="1" s="9">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Universal Epic Universe</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Monsters Unchained: The Frankenstein Experiment</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="386" ht="15.75" customHeight="1" s="9">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Universal Epic Universe</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Mario Kart: Bowser's Challenge</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="387" ht="15.75" customHeight="1" s="9">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Universal Epic Universe</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Mine-Cart Madness</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="388" ht="15.75" customHeight="1" s="9">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Universal Epic Universe</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Hiccup's Wing Gliders</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="389" ht="15.75" customHeight="1" s="9">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Magic Kingdom</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>TRON Lightcycle / Run</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="390" ht="15.75" customHeight="1" s="9">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Magic Kingdom</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Seven Dwarfs Mine Train</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="391" ht="15.75" customHeight="1" s="9">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Disney's Hollywood Studios</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Star Wars: Rise of the Resistance</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="392" ht="15.75" customHeight="1" s="9">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>EPCOT</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Guardians of the Galaxy: Cosmic Rewind</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="393" ht="15.75" customHeight="1" s="9">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Disney's Animal Kingdom</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Avatar Flight of Passage</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="394" ht="15.75" customHeight="1" s="9">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cedar Point</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Steel Vengeance</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="395" ht="15.75" customHeight="1" s="9">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Cedar Point</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Millennium Force</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="396" ht="15.75" customHeight="1" s="9">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Cedar Point</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Maverick</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="397" ht="15.75" customHeight="1" s="9">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Six Flags Magic Mountain</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="398" ht="15.75" customHeight="1" s="9">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Six Flags Magic Mountain</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Twisted Colossus</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="399" ht="15.75" customHeight="1" s="9">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Six Flags Magic Mountain</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Wonder Woman Flight of Courage</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="400" ht="15.75" customHeight="1" s="9">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Busch Gardens Tampa Bay</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Iron Gwazi</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="401" ht="15.75" customHeight="1" s="9">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SeaWorld Orlando</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Mako</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="402" ht="15.75" customHeight="1" s="9">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Knott's Berry Farm</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GhostRider</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="403" ht="15.75" customHeight="1" s="9">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>États-Unis</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Dollywood</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Lightning Rod</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>24</v>
+      </c>
+    </row>
     <row r="404" ht="15.75" customHeight="1" s="9"/>
     <row r="405" ht="15.75" customHeight="1" s="9"/>
     <row r="406" ht="15.75" customHeight="1" s="9"/>
